--- a/data/trans_bre/P32A-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P32A-Provincia-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,78; -1,28</t>
+          <t>-7,18; -0,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,15; -1,44</t>
+          <t>-15,12; -0,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 4,39</t>
+          <t>-6,33; 4,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 0,0</t>
+          <t>-4,64; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-92,29; 3,77</t>
+          <t>-91,28; 8,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-89,91; 188,34</t>
+          <t>-100,0; 213,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,97; -0,9</t>
+          <t>-5,15; -0,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 1,35</t>
+          <t>-3,24; 1,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 2,16</t>
+          <t>-3,72; 2,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,86; 0,0</t>
+          <t>-2,71; 0,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 645,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 0,0</t>
+          <t>-2,71; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 0,0</t>
+          <t>-2,02; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 0,0</t>
+          <t>-2,13; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 0,11</t>
+          <t>-5,94; 0,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 56,43</t>
+          <t>-100,0; 77,48</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 1,93</t>
+          <t>-1,65; 2,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 0,0</t>
+          <t>-3,52; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 0,0</t>
+          <t>-3,0; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 1,69</t>
+          <t>-2,32; 2,01</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 351,57</t>
+          <t>-91,94; —</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 0,0</t>
+          <t>-4,38; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 2,73</t>
+          <t>-6,6; 2,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,36; -1,01</t>
+          <t>-8,45; -1,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,67</t>
+          <t>0,0; 23,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 4,2</t>
+          <t>-1,15; 4,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 4,61</t>
+          <t>-1,91; 4,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 3,14</t>
+          <t>-3,5; 3,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 296,88</t>
+          <t>-85,58; 220,41</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 0,0</t>
+          <t>-2,09; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,18; -0,31</t>
+          <t>-4,15; -0,23</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 0,63</t>
+          <t>-4,85; 0,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 3,12</t>
+          <t>-3,84; 2,75</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 82,77</t>
+          <t>-100,0; 44,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-88,92; 46,53</t>
+          <t>-89,08; 41,18</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-90,79; 201,73</t>
+          <t>-88,98; 166,82</t>
         </is>
       </c>
     </row>
@@ -1360,22 +1360,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 2,23</t>
+          <t>-0,69; 2,09</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,48; -0,45</t>
+          <t>-3,61; -0,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 3,21</t>
+          <t>-0,05; 3,24</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 2,3</t>
+          <t>-1,74; 2,1</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,33; -0,16</t>
+          <t>-1,32; -0,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,57; -0,69</t>
+          <t>-2,6; -0,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 0,33</t>
+          <t>-1,63; 0,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,77</t>
+          <t>-1,49; 0,71</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-92,29; -2,0</t>
+          <t>-93,63; 7,88</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-86,49; -29,94</t>
+          <t>-86,29; -24,03</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-65,7; 24,37</t>
+          <t>-66,2; 21,08</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-67,47; 53,64</t>
+          <t>-66,61; 50,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P32A-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P32A-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-1,29</t>
+          <t>-1,15</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,18; -0,69</t>
+          <t>-6,72; -1,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,12; -0,65</t>
+          <t>-15,17; -1,29</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 4,62</t>
+          <t>-7,05; 4,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 0,0</t>
+          <t>-3,9; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,12 +685,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-91,28; 8,93</t>
+          <t>-91,5; -5,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 213,95</t>
+          <t>-89,14; 246,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,53</t>
+          <t>-0,54</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,15; -0,9</t>
+          <t>-5,37; -0,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 1,07</t>
+          <t>-2,86; 1,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 2,71</t>
+          <t>-3,75; 2,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 0,0</t>
+          <t>-2,52; 0,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 645,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-2,83</t>
+          <t>-3,06</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-70,86%</t>
+          <t>-71,83%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 0,0</t>
+          <t>-2,45; 0,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 0,0</t>
+          <t>-2,57; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 0,0</t>
+          <t>-2,26; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,94; 0,2</t>
+          <t>-6,25; -0,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 77,48</t>
+          <t>-100,0; 32,75</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,02</t>
+          <t>0,13</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-1,43%</t>
+          <t>10,7%</t>
         </is>
       </c>
     </row>
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 2,13</t>
+          <t>-1,63; 2,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 0,0</t>
+          <t>-3,55; 0,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 0,0</t>
+          <t>-2,74; 0,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 2,01</t>
+          <t>-1,59; 2,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-91,94; —</t>
+          <t>-86,55; —</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,13</t>
+          <t>4,33</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 0,0</t>
+          <t>-4,64; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,6; 2,66</t>
+          <t>-6,72; 2,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,45; -1,01</t>
+          <t>-8,46; -1,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,83</t>
+          <t>0,0; 23,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,72</t>
+          <t>-0,63</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-23,76%</t>
+          <t>-21,78%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 0,0</t>
+          <t>-4,49; 0,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 4,33</t>
+          <t>-1,14; 4,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 4,83</t>
+          <t>-1,92; 5,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 3,22</t>
+          <t>-3,8; 3,21</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-85,58; 220,41</t>
+          <t>-100,0; 246,4</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,21</t>
+          <t>2,97</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-9,58%</t>
+          <t>116,36%</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 0,0</t>
+          <t>-2,03; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,15; -0,23</t>
+          <t>-4,04; -0,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 0,52</t>
+          <t>-4,79; 0,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 2,75</t>
+          <t>-0,42; 7,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1285,17 +1285,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 44,85</t>
+          <t>-100,0; 91,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-89,08; 41,18</t>
+          <t>-89,37; 49,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-88,98; 166,82</t>
+          <t>-24,95; 482,86</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>-0,26</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>-27,63%</t>
+          <t>-26,89%</t>
         </is>
       </c>
     </row>
@@ -1360,22 +1360,22 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,09</t>
+          <t>-0,67; 2,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-3,61; -0,46</t>
+          <t>-3,78; -0,53</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 3,24</t>
+          <t>-0,21; 3,41</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,1</t>
+          <t>-1,68; 1,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>0,34</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>-22,18%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,32; -0,06</t>
+          <t>-1,32; -0,13</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,6; -0,63</t>
+          <t>-2,7; -0,74</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 0,33</t>
+          <t>-1,46; 0,42</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,71</t>
+          <t>-0,75; 1,67</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-93,63; 7,88</t>
+          <t>-92,11; 2,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-86,29; -24,03</t>
+          <t>-86,71; -28,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-66,2; 21,08</t>
+          <t>-63,82; 27,84</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-66,61; 50,79</t>
+          <t>-36,37; 115,8</t>
         </is>
       </c>
     </row>
